--- a/examples/HFP_john+sally.xlsx
+++ b/examples/HFP_john+sally.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,35 +449,40 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>net inv</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>taxable ctrb</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>401k ctrb</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Roth 401k ctrb</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>IRA ctrb</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Roth IRA ctrb</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Roth conv</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -491,13 +496,16 @@
       <c r="C2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -507,13 +515,16 @@
       <c r="C3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -523,13 +534,16 @@
       <c r="C4" t="n">
         <v>0</v>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -539,13 +553,16 @@
       <c r="C5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -555,13 +572,16 @@
       <c r="C6" t="n">
         <v>0</v>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -573,15 +593,18 @@
       <c r="C7" t="n">
         <v>0</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="n">
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
         <v>15000</v>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -591,13 +614,16 @@
       <c r="C8" t="n">
         <v>0</v>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -607,13 +633,16 @@
       <c r="C9" t="n">
         <v>0</v>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -623,13 +652,16 @@
       <c r="C10" t="n">
         <v>0</v>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -639,13 +671,16 @@
       <c r="C11" t="n">
         <v>0</v>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -655,13 +690,16 @@
       <c r="C12" t="n">
         <v>0</v>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -671,13 +709,16 @@
       <c r="C13" t="n">
         <v>0</v>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -687,13 +728,16 @@
       <c r="C14" t="n">
         <v>0</v>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -703,13 +747,16 @@
       <c r="C15" t="n">
         <v>0</v>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -719,13 +766,16 @@
       <c r="C16" t="n">
         <v>0</v>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -735,13 +785,16 @@
       <c r="C17" t="n">
         <v>0</v>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -751,13 +804,16 @@
       <c r="C18" t="n">
         <v>0</v>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -767,13 +823,16 @@
       <c r="C19" t="n">
         <v>0</v>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -783,13 +842,16 @@
       <c r="C20" t="n">
         <v>0</v>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -799,13 +861,16 @@
       <c r="C21" t="n">
         <v>0</v>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -815,13 +880,16 @@
       <c r="C22" t="n">
         <v>0</v>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -831,13 +899,16 @@
       <c r="C23" t="n">
         <v>0</v>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -847,13 +918,16 @@
       <c r="C24" t="n">
         <v>0</v>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -863,13 +937,16 @@
       <c r="C25" t="n">
         <v>0</v>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -879,13 +956,16 @@
       <c r="C26" t="n">
         <v>0</v>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -895,13 +975,16 @@
       <c r="C27" t="n">
         <v>0</v>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -911,13 +994,16 @@
       <c r="C28" t="n">
         <v>0</v>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -927,13 +1013,16 @@
       <c r="C29" t="n">
         <v>0</v>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -943,13 +1032,16 @@
       <c r="C30" t="n">
         <v>0</v>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -959,13 +1051,16 @@
       <c r="C31" t="n">
         <v>0</v>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -975,13 +1070,16 @@
       <c r="C32" t="n">
         <v>0</v>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -991,13 +1089,16 @@
       <c r="C33" t="n">
         <v>0</v>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1007,13 +1108,16 @@
       <c r="C34" t="n">
         <v>0</v>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1023,13 +1127,16 @@
       <c r="C35" t="n">
         <v>0</v>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1039,13 +1146,16 @@
       <c r="C36" t="n">
         <v>0</v>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1055,13 +1165,16 @@
       <c r="C37" t="n">
         <v>0</v>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1074,7 +1187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1095,35 +1208,40 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>net inv</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>taxable ctrb</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>401k ctrb</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Roth 401k ctrb</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>IRA ctrb</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Roth IRA ctrb</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Roth conv</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -1137,13 +1255,16 @@
       <c r="C2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1153,13 +1274,16 @@
       <c r="C3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1169,13 +1293,16 @@
       <c r="C4" t="n">
         <v>0</v>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1185,13 +1312,16 @@
       <c r="C5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,13 +1331,16 @@
       <c r="C6" t="n">
         <v>0</v>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1217,13 +1350,16 @@
       <c r="C7" t="n">
         <v>0</v>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1233,13 +1369,16 @@
       <c r="C8" t="n">
         <v>0</v>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1249,13 +1388,16 @@
       <c r="C9" t="n">
         <v>0</v>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1265,13 +1407,16 @@
       <c r="C10" t="n">
         <v>0</v>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1281,13 +1426,16 @@
       <c r="C11" t="n">
         <v>0</v>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1297,13 +1445,16 @@
       <c r="C12" t="n">
         <v>0</v>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1313,13 +1464,16 @@
       <c r="C13" t="n">
         <v>0</v>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1329,13 +1483,16 @@
       <c r="C14" t="n">
         <v>0</v>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1345,13 +1502,16 @@
       <c r="C15" t="n">
         <v>0</v>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1361,13 +1521,16 @@
       <c r="C16" t="n">
         <v>0</v>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1377,13 +1540,16 @@
       <c r="C17" t="n">
         <v>0</v>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1393,13 +1559,16 @@
       <c r="C18" t="n">
         <v>0</v>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1409,13 +1578,16 @@
       <c r="C19" t="n">
         <v>0</v>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1425,13 +1597,16 @@
       <c r="C20" t="n">
         <v>0</v>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1441,13 +1616,16 @@
       <c r="C21" t="n">
         <v>0</v>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1457,13 +1635,16 @@
       <c r="C22" t="n">
         <v>0</v>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1473,13 +1654,16 @@
       <c r="C23" t="n">
         <v>0</v>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1489,13 +1673,16 @@
       <c r="C24" t="n">
         <v>0</v>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1505,13 +1692,16 @@
       <c r="C25" t="n">
         <v>0</v>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1521,13 +1711,16 @@
       <c r="C26" t="n">
         <v>0</v>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1537,13 +1730,16 @@
       <c r="C27" t="n">
         <v>0</v>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1553,13 +1749,16 @@
       <c r="C28" t="n">
         <v>0</v>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1569,13 +1768,16 @@
       <c r="C29" t="n">
         <v>0</v>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1585,13 +1787,16 @@
       <c r="C30" t="n">
         <v>0</v>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1601,13 +1806,16 @@
       <c r="C31" t="n">
         <v>0</v>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1617,13 +1825,16 @@
       <c r="C32" t="n">
         <v>0</v>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1633,13 +1844,16 @@
       <c r="C33" t="n">
         <v>0</v>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1649,13 +1863,16 @@
       <c r="C34" t="n">
         <v>0</v>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1665,13 +1882,16 @@
       <c r="C35" t="n">
         <v>0</v>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1681,13 +1901,16 @@
       <c r="C36" t="n">
         <v>0</v>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1697,13 +1920,16 @@
       <c r="C37" t="n">
         <v>0</v>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1713,13 +1939,16 @@
       <c r="C38" t="n">
         <v>0</v>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1729,13 +1958,16 @@
       <c r="C39" t="n">
         <v>0</v>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1745,13 +1977,16 @@
       <c r="C40" t="n">
         <v>0</v>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/examples/HFP_john+sally.xlsx
+++ b/examples/HFP_john+sally.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,6 +485,11 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>HSA ctrb</t>
         </is>
       </c>
     </row>
@@ -506,6 +511,9 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -525,6 +533,9 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -544,6 +555,9 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -563,6 +577,9 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -582,6 +599,9 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -605,6 +625,9 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>4000</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -624,6 +647,9 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>4000</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -643,6 +669,9 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -662,6 +691,9 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -681,6 +713,9 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -700,6 +735,9 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -719,6 +757,9 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -738,6 +779,9 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -757,6 +801,9 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -776,6 +823,9 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -795,6 +845,9 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -814,6 +867,9 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -833,6 +889,9 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -852,6 +911,9 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -871,6 +933,9 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -890,6 +955,9 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -909,6 +977,9 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -928,6 +999,9 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -947,6 +1021,9 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -966,6 +1043,9 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -985,6 +1065,9 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1004,6 +1087,9 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1023,6 +1109,9 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1042,6 +1131,9 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1061,6 +1153,9 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1080,6 +1175,9 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1099,6 +1197,9 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1118,6 +1219,9 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1137,6 +1241,9 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1156,6 +1263,9 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1175,6 +1285,9 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1187,7 +1300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1244,6 +1357,11 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>HSA ctrb</t>
         </is>
       </c>
     </row>
@@ -1265,6 +1383,9 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1284,6 +1405,9 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1303,6 +1427,9 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1322,6 +1449,9 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1341,6 +1471,9 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1360,6 +1493,9 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>4000</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1515,9 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>4000</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1398,6 +1537,9 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1417,6 +1559,9 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1436,6 +1581,9 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1455,6 +1603,9 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1474,6 +1625,9 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1493,6 +1647,9 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1512,6 +1669,9 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1531,6 +1691,9 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1550,6 +1713,9 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1569,6 +1735,9 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1588,6 +1757,9 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1607,6 +1779,9 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1626,6 +1801,9 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1645,6 +1823,9 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1664,6 +1845,9 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1683,6 +1867,9 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1702,6 +1889,9 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1721,6 +1911,9 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1740,6 +1933,9 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1759,6 +1955,9 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1778,6 +1977,9 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1797,6 +1999,9 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1816,6 +2021,9 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1835,6 +2043,9 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1854,6 +2065,9 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1873,6 +2087,9 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1892,6 +2109,9 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1911,6 +2131,9 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1930,6 +2153,9 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1949,6 +2175,9 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1968,6 +2197,9 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1987,6 +2219,9 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/examples/HFP_john+sally.xlsx
+++ b/examples/HFP_john+sally.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="John" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sally" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debts" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixed Assets" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="John" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sally" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Debts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Fixed Assets" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,66 +416,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>anticipated wages</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>other inc</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>net inv</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>taxable ctrb</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>401k ctrb</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Roth 401k ctrb</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>IRA ctrb</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Roth IRA ctrb</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Roth conv</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>QCD</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
@@ -510,8 +503,11 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -532,8 +528,11 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -554,8 +553,11 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -576,8 +578,11 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -598,8 +603,11 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -624,8 +632,11 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -646,8 +657,11 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -668,8 +682,11 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -690,8 +707,11 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -712,8 +732,11 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -734,8 +757,11 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -756,8 +782,11 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -778,8 +807,11 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -800,8 +832,11 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="n">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -822,8 +857,11 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -844,8 +882,11 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -866,8 +907,11 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="n">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -888,8 +932,11 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="n">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -910,8 +957,11 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="n">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -932,8 +982,11 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="n">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -954,8 +1007,11 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="n">
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -976,8 +1032,11 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="n">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -998,8 +1057,11 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="n">
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1020,8 +1082,11 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="n">
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1042,8 +1107,11 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="n">
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1064,8 +1132,11 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="n">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1086,8 +1157,11 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="n">
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1108,8 +1182,11 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="n">
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1130,8 +1207,11 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="n">
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1152,8 +1232,11 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="n">
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1174,8 +1257,11 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="n">
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1196,8 +1282,11 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="n">
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1218,8 +1307,11 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="n">
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1240,8 +1332,11 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="n">
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1262,8 +1357,11 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="n">
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1284,8 +1382,11 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="n">
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1300,66 +1401,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>anticipated wages</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>other inc</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>net inv</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>taxable ctrb</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>401k ctrb</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Roth 401k ctrb</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>IRA ctrb</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Roth IRA ctrb</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Roth conv</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>QCD</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
@@ -1382,8 +1488,11 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1404,8 +1513,11 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1426,8 +1538,11 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1448,8 +1563,11 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1470,8 +1588,11 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1492,8 +1613,11 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -1514,8 +1638,11 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -1536,8 +1663,11 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1558,8 +1688,11 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1580,8 +1713,11 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1602,8 +1738,11 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1624,8 +1763,11 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1646,8 +1788,11 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1668,8 +1813,11 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="n">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1690,8 +1838,11 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1712,8 +1863,11 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1734,8 +1888,11 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="n">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1756,8 +1913,11 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="n">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1778,8 +1938,11 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="n">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1800,8 +1963,11 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="n">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1822,8 +1988,11 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="n">
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1844,8 +2013,11 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="n">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1866,8 +2038,11 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="n">
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1888,8 +2063,11 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="n">
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1910,8 +2088,11 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="n">
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1932,8 +2113,11 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="n">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1954,8 +2138,11 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="n">
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1976,8 +2163,11 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="n">
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1998,8 +2188,11 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="n">
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2020,8 +2213,11 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="n">
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2042,8 +2238,11 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="n">
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2064,8 +2263,11 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="n">
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2086,8 +2288,11 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="n">
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2108,8 +2313,11 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="n">
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2130,8 +2338,11 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="n">
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2152,8 +2363,11 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="n">
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2174,8 +2388,11 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="n">
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2196,8 +2413,11 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="n">
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2218,8 +2438,11 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="n">
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2238,37 +2461,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>term</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>rate</t>
         </is>
@@ -2289,47 +2512,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>basis</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>rate</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>yod</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>commission</t>
         </is>

--- a/examples/HFP_john+sally.xlsx
+++ b/examples/HFP_john+sally.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,15 +472,20 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>Roth conv fixed</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>QCD</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
@@ -490,24 +495,16 @@
       <c r="A2" t="n">
         <v>2021</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -515,24 +512,16 @@
       <c r="A3" t="n">
         <v>2022</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -540,24 +529,16 @@
       <c r="A4" t="n">
         <v>2023</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="n">
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -565,24 +546,16 @@
       <c r="A5" t="n">
         <v>2024</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="n">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -590,24 +563,16 @@
       <c r="A6" t="n">
         <v>2025</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -624,19 +589,13 @@
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
         <v>15000</v>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="n">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -644,24 +603,16 @@
       <c r="A8" t="n">
         <v>2027</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="n">
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -669,24 +620,16 @@
       <c r="A9" t="n">
         <v>2028</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="n">
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -694,24 +637,16 @@
       <c r="A10" t="n">
         <v>2029</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="n">
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -719,24 +654,16 @@
       <c r="A11" t="n">
         <v>2030</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -744,24 +671,16 @@
       <c r="A12" t="n">
         <v>2031</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="n">
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -769,24 +688,16 @@
       <c r="A13" t="n">
         <v>2032</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="n">
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -794,24 +705,16 @@
       <c r="A14" t="n">
         <v>2033</v>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="n">
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -819,24 +722,16 @@
       <c r="A15" t="n">
         <v>2034</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="n">
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -844,24 +739,16 @@
       <c r="A16" t="n">
         <v>2035</v>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -869,24 +756,16 @@
       <c r="A17" t="n">
         <v>2036</v>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="n">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -894,24 +773,16 @@
       <c r="A18" t="n">
         <v>2037</v>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="n">
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -919,24 +790,16 @@
       <c r="A19" t="n">
         <v>2038</v>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -944,24 +807,16 @@
       <c r="A20" t="n">
         <v>2039</v>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="n">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -969,24 +824,16 @@
       <c r="A21" t="n">
         <v>2040</v>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="n">
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -994,24 +841,16 @@
       <c r="A22" t="n">
         <v>2041</v>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="n">
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1019,24 +858,16 @@
       <c r="A23" t="n">
         <v>2042</v>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="n">
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1044,24 +875,16 @@
       <c r="A24" t="n">
         <v>2043</v>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="n">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1069,24 +892,16 @@
       <c r="A25" t="n">
         <v>2044</v>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="n">
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1094,24 +909,16 @@
       <c r="A26" t="n">
         <v>2045</v>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="n">
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1119,24 +926,16 @@
       <c r="A27" t="n">
         <v>2046</v>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="n">
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1144,24 +943,16 @@
       <c r="A28" t="n">
         <v>2047</v>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="n">
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1169,24 +960,16 @@
       <c r="A29" t="n">
         <v>2048</v>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="n">
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1194,24 +977,16 @@
       <c r="A30" t="n">
         <v>2049</v>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="n">
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1219,24 +994,16 @@
       <c r="A31" t="n">
         <v>2050</v>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="n">
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1244,24 +1011,16 @@
       <c r="A32" t="n">
         <v>2051</v>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="n">
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1269,24 +1028,16 @@
       <c r="A33" t="n">
         <v>2052</v>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="n">
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1294,24 +1045,16 @@
       <c r="A34" t="n">
         <v>2053</v>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="n">
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1319,24 +1062,16 @@
       <c r="A35" t="n">
         <v>2054</v>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="n">
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1344,24 +1079,16 @@
       <c r="A36" t="n">
         <v>2055</v>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="n">
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1369,24 +1096,16 @@
       <c r="A37" t="n">
         <v>2056</v>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="n">
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1401,7 +1120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:N40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1457,15 +1176,20 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>Roth conv fixed</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>QCD</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
@@ -1475,24 +1199,16 @@
       <c r="A2" t="n">
         <v>2021</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1500,24 +1216,16 @@
       <c r="A3" t="n">
         <v>2022</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1525,24 +1233,16 @@
       <c r="A4" t="n">
         <v>2023</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="n">
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1550,24 +1250,16 @@
       <c r="A5" t="n">
         <v>2024</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="n">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1575,24 +1267,16 @@
       <c r="A6" t="n">
         <v>2025</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1600,24 +1284,16 @@
       <c r="A7" t="n">
         <v>2026</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="n">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -1625,24 +1301,16 @@
       <c r="A8" t="n">
         <v>2027</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="n">
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -1650,24 +1318,16 @@
       <c r="A9" t="n">
         <v>2028</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="n">
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1675,24 +1335,16 @@
       <c r="A10" t="n">
         <v>2029</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="n">
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1700,24 +1352,16 @@
       <c r="A11" t="n">
         <v>2030</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1725,24 +1369,16 @@
       <c r="A12" t="n">
         <v>2031</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="n">
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1750,24 +1386,16 @@
       <c r="A13" t="n">
         <v>2032</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="n">
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1775,24 +1403,16 @@
       <c r="A14" t="n">
         <v>2033</v>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="n">
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1800,24 +1420,16 @@
       <c r="A15" t="n">
         <v>2034</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="n">
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1825,24 +1437,16 @@
       <c r="A16" t="n">
         <v>2035</v>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1850,24 +1454,16 @@
       <c r="A17" t="n">
         <v>2036</v>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="n">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1875,24 +1471,16 @@
       <c r="A18" t="n">
         <v>2037</v>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="n">
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1900,24 +1488,16 @@
       <c r="A19" t="n">
         <v>2038</v>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1925,24 +1505,16 @@
       <c r="A20" t="n">
         <v>2039</v>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="n">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1950,24 +1522,16 @@
       <c r="A21" t="n">
         <v>2040</v>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="n">
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1975,24 +1539,16 @@
       <c r="A22" t="n">
         <v>2041</v>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="n">
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2000,24 +1556,16 @@
       <c r="A23" t="n">
         <v>2042</v>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="n">
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2025,24 +1573,16 @@
       <c r="A24" t="n">
         <v>2043</v>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="n">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2050,24 +1590,16 @@
       <c r="A25" t="n">
         <v>2044</v>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="n">
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2075,24 +1607,16 @@
       <c r="A26" t="n">
         <v>2045</v>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="n">
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2100,24 +1624,16 @@
       <c r="A27" t="n">
         <v>2046</v>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="n">
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2125,24 +1641,16 @@
       <c r="A28" t="n">
         <v>2047</v>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="n">
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2150,24 +1658,16 @@
       <c r="A29" t="n">
         <v>2048</v>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="n">
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2175,24 +1675,16 @@
       <c r="A30" t="n">
         <v>2049</v>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="n">
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2200,24 +1692,16 @@
       <c r="A31" t="n">
         <v>2050</v>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="n">
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2225,24 +1709,16 @@
       <c r="A32" t="n">
         <v>2051</v>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="n">
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2250,24 +1726,16 @@
       <c r="A33" t="n">
         <v>2052</v>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="n">
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2275,24 +1743,16 @@
       <c r="A34" t="n">
         <v>2053</v>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="n">
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2300,24 +1760,16 @@
       <c r="A35" t="n">
         <v>2054</v>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="n">
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2325,24 +1777,16 @@
       <c r="A36" t="n">
         <v>2055</v>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="n">
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2350,24 +1794,16 @@
       <c r="A37" t="n">
         <v>2056</v>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="n">
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2375,24 +1811,16 @@
       <c r="A38" t="n">
         <v>2057</v>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="n">
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2400,24 +1828,16 @@
       <c r="A39" t="n">
         <v>2058</v>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="n">
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2425,24 +1845,16 @@
       <c r="A40" t="n">
         <v>2059</v>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="n">
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
         <v>0</v>
       </c>
     </row>
